--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -464,34 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>16.71746</v>
+        <v>17.07565</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86241</v>
+        <v>16.67387</v>
       </c>
       <c r="E2" t="n">
-        <v>17.07421</v>
+        <v>16.71549</v>
       </c>
       <c r="F2" t="n">
-        <v>55.51085</v>
+        <v>42.44104</v>
       </c>
       <c r="G2" t="n">
-        <v>43.22322</v>
+        <v>0.0508</v>
       </c>
       <c r="H2" t="n">
-        <v>84.05328</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05125</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.86114</v>
+        <v>1.82742</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.78798</v>
+        <v>16.93187</v>
       </c>
       <c r="D3" t="n">
-        <v>16.54723</v>
+        <v>16.67585</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69407</v>
+        <v>16.73204</v>
       </c>
       <c r="F3" t="n">
-        <v>54.62573</v>
+        <v>43.38535</v>
       </c>
       <c r="G3" t="n">
-        <v>43.44233</v>
+        <v>0.05015</v>
       </c>
       <c r="H3" t="n">
-        <v>84.86884999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.84718</v>
+        <v>1.85693</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.01234</v>
+        <v>17.09514</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90899</v>
+        <v>16.87283</v>
       </c>
       <c r="E4" t="n">
-        <v>17.06391</v>
+        <v>16.91339</v>
       </c>
       <c r="F4" t="n">
-        <v>57.44581</v>
+        <v>42.44576</v>
       </c>
       <c r="G4" t="n">
-        <v>42.15815</v>
+        <v>0.0509</v>
       </c>
       <c r="H4" t="n">
-        <v>86.17178</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05127</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.84144</v>
+        <v>1.81905</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.86283</v>
+        <v>17.17328</v>
       </c>
       <c r="D5" t="n">
-        <v>16.48098</v>
+        <v>16.72313</v>
       </c>
       <c r="E5" t="n">
-        <v>16.89168</v>
+        <v>16.79002</v>
       </c>
       <c r="F5" t="n">
-        <v>55.55176</v>
+        <v>43.64734</v>
       </c>
       <c r="G5" t="n">
-        <v>42.99793</v>
+        <v>0.05118</v>
       </c>
       <c r="H5" t="n">
-        <v>84.94575</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05091</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.83321</v>
+        <v>1.82526</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.75426</v>
+        <v>17.19079</v>
       </c>
       <c r="D6" t="n">
-        <v>16.83415</v>
+        <v>16.79396</v>
       </c>
       <c r="E6" t="n">
-        <v>16.9303</v>
+        <v>17.06937</v>
       </c>
       <c r="F6" t="n">
-        <v>56.16855</v>
+        <v>43.28799</v>
       </c>
       <c r="G6" t="n">
-        <v>43.02605</v>
+        <v>0.05147</v>
       </c>
       <c r="H6" t="n">
-        <v>85.60468</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05144</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.86221</v>
+        <v>1.82324</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.21713</v>
+        <v>17.22895</v>
       </c>
       <c r="D7" t="n">
-        <v>16.58898</v>
+        <v>16.5321</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02291</v>
+        <v>16.90794</v>
       </c>
       <c r="F7" t="n">
-        <v>56.66134</v>
+        <v>42.45762</v>
       </c>
       <c r="G7" t="n">
-        <v>42.85831</v>
+        <v>0.05141</v>
       </c>
       <c r="H7" t="n">
-        <v>85.08793</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05127</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.84643</v>
+        <v>1.83864</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83457</v>
+        <v>16.99231</v>
       </c>
       <c r="D8" t="n">
-        <v>16.74449</v>
+        <v>16.72677</v>
       </c>
       <c r="E8" t="n">
-        <v>16.91668</v>
+        <v>16.93641</v>
       </c>
       <c r="F8" t="n">
-        <v>57.103</v>
+        <v>42.63613</v>
       </c>
       <c r="G8" t="n">
-        <v>43.47509</v>
+        <v>0.0521</v>
       </c>
       <c r="H8" t="n">
-        <v>85.88942</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05054</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.84433</v>
+        <v>1.86624</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.7932</v>
+        <v>16.93499</v>
       </c>
       <c r="D9" t="n">
-        <v>16.9224</v>
+        <v>16.56127</v>
       </c>
       <c r="E9" t="n">
-        <v>17.29546</v>
+        <v>16.66832</v>
       </c>
       <c r="F9" t="n">
-        <v>57.3365</v>
+        <v>42.63077</v>
       </c>
       <c r="G9" t="n">
-        <v>42.61794</v>
+        <v>0.05099</v>
       </c>
       <c r="H9" t="n">
-        <v>83.60984999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05227</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.8565</v>
+        <v>1.85534</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +655,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.20197</v>
+        <v>17.11954</v>
       </c>
       <c r="D10" t="n">
-        <v>16.50708</v>
+        <v>16.5423</v>
       </c>
       <c r="E10" t="n">
-        <v>16.76618</v>
+        <v>16.95446</v>
       </c>
       <c r="F10" t="n">
-        <v>56.04917</v>
+        <v>43.38668</v>
       </c>
       <c r="G10" t="n">
-        <v>42.03803</v>
+        <v>0.05209</v>
       </c>
       <c r="H10" t="n">
-        <v>87.10286000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05109</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8498</v>
+        <v>1.86193</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +691,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -792,32 +713,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.89382</v>
+        <v>17.2779</v>
       </c>
       <c r="D12" t="n">
-        <v>16.69771</v>
+        <v>16.79319</v>
       </c>
       <c r="E12" t="n">
-        <v>16.76259</v>
+        <v>16.79554</v>
       </c>
       <c r="F12" t="n">
-        <v>57.33565</v>
+        <v>43.05131</v>
       </c>
       <c r="G12" t="n">
-        <v>42.86699</v>
+        <v>0.05083</v>
       </c>
       <c r="H12" t="n">
-        <v>87.74963</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05151</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.81262</v>
+        <v>1.80537</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.18462</v>
+        <v>17.11451</v>
       </c>
       <c r="D13" t="n">
-        <v>16.94911</v>
+        <v>16.53606</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7759</v>
+        <v>16.8778</v>
       </c>
       <c r="F13" t="n">
-        <v>55.21589</v>
+        <v>42.10813</v>
       </c>
       <c r="G13" t="n">
-        <v>43.91594</v>
+        <v>0.05125</v>
       </c>
       <c r="H13" t="n">
-        <v>86.8274</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05051</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.85475</v>
+        <v>1.85084</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +767,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.87646</v>
+        <v>17.06491</v>
       </c>
       <c r="D14" t="n">
-        <v>16.15072</v>
+        <v>16.71833</v>
       </c>
       <c r="E14" t="n">
-        <v>16.66388</v>
+        <v>16.9254</v>
       </c>
       <c r="F14" t="n">
-        <v>55.57663</v>
+        <v>43.87052</v>
       </c>
       <c r="G14" t="n">
-        <v>43.17953</v>
+        <v>0.0504</v>
       </c>
       <c r="H14" t="n">
-        <v>85.94172</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.05127</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.83575</v>
+        <v>1.82704</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +792,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.11128</v>
+        <v>17.20082</v>
       </c>
       <c r="D15" t="n">
-        <v>17.15668</v>
+        <v>16.78983</v>
       </c>
       <c r="E15" t="n">
-        <v>16.9154</v>
+        <v>17.07205</v>
       </c>
       <c r="F15" t="n">
-        <v>56.2638</v>
+        <v>43.04982</v>
       </c>
       <c r="G15" t="n">
-        <v>43.16822</v>
+        <v>0.0506</v>
       </c>
       <c r="H15" t="n">
-        <v>85.20922</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05118</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.84214</v>
+        <v>1.84309</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +817,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.20549</v>
+        <v>17.17053</v>
       </c>
       <c r="D16" t="n">
-        <v>16.82864</v>
+        <v>16.77795</v>
       </c>
       <c r="E16" t="n">
-        <v>16.84275</v>
+        <v>16.94036</v>
       </c>
       <c r="F16" t="n">
-        <v>56.33012</v>
+        <v>42.44819</v>
       </c>
       <c r="G16" t="n">
-        <v>43.42889</v>
+        <v>0.05028</v>
       </c>
       <c r="H16" t="n">
-        <v>84.26742</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05182</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.84909</v>
+        <v>1.84825</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +842,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.909</v>
+        <v>16.91952</v>
       </c>
       <c r="D17" t="n">
-        <v>16.66492</v>
+        <v>16.76759</v>
       </c>
       <c r="E17" t="n">
-        <v>16.87283</v>
+        <v>16.91748</v>
       </c>
       <c r="F17" t="n">
-        <v>54.12274</v>
+        <v>42.99174</v>
       </c>
       <c r="G17" t="n">
-        <v>43.57128</v>
+        <v>0.05126</v>
       </c>
       <c r="H17" t="n">
-        <v>86.33719000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05214</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.83543</v>
+        <v>1.8447</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +867,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.81449</v>
+        <v>16.93044</v>
       </c>
       <c r="D18" t="n">
-        <v>17.26687</v>
+        <v>16.78346</v>
       </c>
       <c r="E18" t="n">
-        <v>16.99709</v>
+        <v>16.92278</v>
       </c>
       <c r="F18" t="n">
-        <v>56.07164</v>
+        <v>43.24663</v>
       </c>
       <c r="G18" t="n">
-        <v>42.94661</v>
+        <v>0.0509</v>
       </c>
       <c r="H18" t="n">
-        <v>87.69135</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05118</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.86066</v>
+        <v>1.85319</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +892,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.08194</v>
+        <v>17.11431</v>
       </c>
       <c r="D19" t="n">
-        <v>16.89839</v>
+        <v>16.68262</v>
       </c>
       <c r="E19" t="n">
-        <v>16.85619</v>
+        <v>16.97985</v>
       </c>
       <c r="F19" t="n">
-        <v>55.70469</v>
+        <v>43.3584</v>
       </c>
       <c r="G19" t="n">
-        <v>42.35031</v>
+        <v>0.05289</v>
       </c>
       <c r="H19" t="n">
-        <v>85.7953</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05153</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.86768</v>
+        <v>1.8189</v>
       </c>
     </row>
     <row r="20">
@@ -1044,258 +917,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.67313</v>
+        <v>16.80014</v>
       </c>
       <c r="D20" t="n">
-        <v>17.07793</v>
+        <v>16.71918</v>
       </c>
       <c r="E20" t="n">
-        <v>16.76901</v>
+        <v>16.75578</v>
       </c>
       <c r="F20" t="n">
-        <v>56.19235</v>
+        <v>42.44637</v>
       </c>
       <c r="G20" t="n">
-        <v>42.68075</v>
+        <v>0.05043</v>
       </c>
       <c r="H20" t="n">
-        <v>87.33277</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05202</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.81121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>16.86556</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16.24202</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.54116</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22.10925</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.17876</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>16.67865</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.27119</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.73955</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22.40273</v>
-      </c>
-      <c r="G23" t="n">
-        <v>34.7496</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>17.01437</v>
-      </c>
-      <c r="D24" t="n">
-        <v>15.93764</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16.60498</v>
-      </c>
-      <c r="F24" t="n">
-        <v>22.10358</v>
-      </c>
-      <c r="G24" t="n">
-        <v>34.94267</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>16.84653</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16.12086</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.54643</v>
-      </c>
-      <c r="F25" t="n">
-        <v>22.26823</v>
-      </c>
-      <c r="G25" t="n">
-        <v>35.06658</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.72872</v>
-      </c>
-      <c r="D26" t="n">
-        <v>16.21282</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.91527</v>
-      </c>
-      <c r="F26" t="n">
-        <v>22.04997</v>
-      </c>
-      <c r="G26" t="n">
-        <v>34.64469</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>17.03225</v>
-      </c>
-      <c r="D27" t="n">
-        <v>15.90365</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.74075</v>
-      </c>
-      <c r="F27" t="n">
-        <v>22.38975</v>
-      </c>
-      <c r="G27" t="n">
-        <v>33.98868</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>16.94439</v>
-      </c>
-      <c r="D28" t="n">
-        <v>16.22731</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.22737</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22.35154</v>
-      </c>
-      <c r="G28" t="n">
-        <v>34.35797</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>16.66895</v>
-      </c>
-      <c r="D29" t="n">
-        <v>15.87775</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.68605</v>
-      </c>
-      <c r="F29" t="n">
-        <v>22.03063</v>
-      </c>
-      <c r="G29" t="n">
-        <v>34.61129</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.8395</v>
-      </c>
-      <c r="D30" t="n">
-        <v>16.56189</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.87357</v>
-      </c>
-      <c r="F30" t="n">
-        <v>21.72126</v>
-      </c>
-      <c r="G30" t="n">
-        <v>35.36812</v>
+        <v>1.86324</v>
       </c>
     </row>
   </sheetData>
